--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-moped-ext-neugeborenes.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-moped-ext-neugeborenes.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T12:12:39+00:00</t>
+    <t>2024-11-05T09:00:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-moped-ext-neugeborenes.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-moped-ext-neugeborenes.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:00:17+00:00</t>
+    <t>2024-11-05T09:16:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-moped-ext-neugeborenes.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-moped-ext-neugeborenes.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:16:22+00:00</t>
+    <t>2024-11-05T10:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-moped-ext-neugeborenes.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-moped-ext-neugeborenes.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T10:26:22+00:00</t>
+    <t>2024-11-06T09:40:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
